--- a/Beneficios.xlsx
+++ b/Beneficios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jguedess\Documents\UiPath\RPA003_CadastroBeneficio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC65E7F-A5A4-4DE1-8DFB-579A3F40CE98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C5FD0C-EEA7-4AFB-9006-7961B20A6870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1872" windowWidth="23040" windowHeight="9036" xr2:uid="{C9276DFF-95B8-4181-805F-DD21EA1202CE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{390954F1-6CA0-4FC0-B51C-44BE43145BAD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="39">
   <si>
     <t>Documento</t>
   </si>
@@ -54,100 +54,106 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Carlos Souza</t>
+    <t>José Rodrigues</t>
   </si>
   <si>
     <t>Masculino</t>
   </si>
   <si>
-    <t>24/01/1956</t>
+    <t>13/03/1949</t>
   </si>
   <si>
     <t>Beneficio cadastrado</t>
   </si>
   <si>
-    <t>Carlos Silva</t>
+    <t>Marcos Oliveira</t>
+  </si>
+  <si>
+    <t>Beneficio cancelado</t>
+  </si>
+  <si>
+    <t>Paulo Lima</t>
+  </si>
+  <si>
+    <t>Maria Souza</t>
   </si>
   <si>
     <t>Feminino</t>
   </si>
   <si>
-    <t>13/02/1941</t>
-  </si>
-  <si>
-    <t>João Souza</t>
-  </si>
-  <si>
-    <t>Beneficio cancelado</t>
-  </si>
-  <si>
-    <t>Ana Lima</t>
+    <t>26/05/1950</t>
+  </si>
+  <si>
+    <t>João Pereira</t>
+  </si>
+  <si>
+    <t>Cancelado</t>
+  </si>
+  <si>
+    <t>Marcos Souza</t>
+  </si>
+  <si>
+    <t>23/11/1951</t>
+  </si>
+  <si>
+    <t>Pendente</t>
+  </si>
+  <si>
+    <t>Fernanda Rodrigues</t>
+  </si>
+  <si>
+    <t>23/02/1956</t>
+  </si>
+  <si>
+    <t>Concluído</t>
+  </si>
+  <si>
+    <t>João Oliveira</t>
+  </si>
+  <si>
+    <t>15/11/1954</t>
+  </si>
+  <si>
+    <t>Paulo Costa</t>
+  </si>
+  <si>
+    <t>21/04/1943</t>
+  </si>
+  <si>
+    <t>Ricardo Costa</t>
+  </si>
+  <si>
+    <t>José Lima</t>
+  </si>
+  <si>
+    <t>17/05/1943</t>
   </si>
   <si>
     <t>Maria Pereira</t>
   </si>
   <si>
-    <t>Marcos Costa</t>
+    <t>25/11/1943</t>
+  </si>
+  <si>
+    <t>Fernanda Costa</t>
+  </si>
+  <si>
+    <t>Carlos Rodrigues</t>
+  </si>
+  <si>
+    <t>23/04/1952</t>
   </si>
   <si>
     <t>Ana Silva</t>
   </si>
   <si>
-    <t>16/04/1958</t>
-  </si>
-  <si>
-    <t>Concluído</t>
-  </si>
-  <si>
-    <t>Paulo Souza</t>
-  </si>
-  <si>
-    <t>Pendente</t>
-  </si>
-  <si>
-    <t>22/10/1942</t>
-  </si>
-  <si>
-    <t>Cancelado</t>
-  </si>
-  <si>
-    <t>Marcos Silva</t>
-  </si>
-  <si>
-    <t>20/04/1954</t>
-  </si>
-  <si>
-    <t>15/07/1941</t>
-  </si>
-  <si>
-    <t>Maria Oliveira</t>
-  </si>
-  <si>
-    <t>22/08/1944</t>
-  </si>
-  <si>
-    <t>18/03/1959</t>
-  </si>
-  <si>
-    <t>Carlos Almeida</t>
-  </si>
-  <si>
-    <t>13/08/1947</t>
-  </si>
-  <si>
-    <t>Fernanda Rodrigues</t>
-  </si>
-  <si>
-    <t>14/05/1959</t>
-  </si>
-  <si>
-    <t>19/01/1941</t>
-  </si>
-  <si>
-    <t>Fernanda Silva</t>
-  </si>
-  <si>
-    <t>Paulo Lima</t>
+    <t>27/06/1953</t>
+  </si>
+  <si>
+    <t>15/05/1946</t>
+  </si>
+  <si>
+    <t>Ricardo Lima</t>
   </si>
 </sst>
 </file>
@@ -519,7 +525,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0168572F-7799-4840-8FCF-1E2568CB1497}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C4951E0-4789-4329-A42C-FA36646C363A}">
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -542,7 +548,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>72837658834</v>
+        <v>77301707328</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
@@ -559,58 +565,58 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>34663025109</v>
+        <v>23206665134</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1">
+        <v>15493</v>
+      </c>
+      <c r="E3" t="s">
         <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>89577770026</v>
+        <v>58401653822</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="1">
-        <v>19001</v>
+        <v>14983</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>66873071307</v>
+        <v>81593843352</v>
       </c>
       <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="1">
-        <v>21370</v>
-      </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>70651878081</v>
+        <v>47414561021</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
@@ -619,177 +625,177 @@
         <v>6</v>
       </c>
       <c r="D6" s="1">
-        <v>18695</v>
+        <v>20123</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>59189285937</v>
+        <v>85407765913</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D7" s="1">
-        <v>20980</v>
+        <v>14825</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>54521863524</v>
+        <v>76947843616</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
+        <v>6</v>
+      </c>
+      <c r="D8" s="1">
+        <v>15494</v>
       </c>
       <c r="E8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>54146690163</v>
+        <v>86333368746</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="1">
-        <v>16774</v>
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>96071350934</v>
+        <v>50278691568</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
         <v>22</v>
-      </c>
-      <c r="E10" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>54036287814</v>
+        <v>72679621567</v>
       </c>
       <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
         <v>24</v>
       </c>
-      <c r="C11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" t="s">
-        <v>25</v>
-      </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>75947408146</v>
+        <v>40556529183</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D12" t="s">
         <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>96252733631</v>
+        <v>32421582677</v>
       </c>
       <c r="B13" t="s">
         <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" t="s">
-        <v>28</v>
+        <v>13</v>
+      </c>
+      <c r="D13" s="1">
+        <v>21164</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>47853883629</v>
+        <v>15614950018</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D14" t="s">
         <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>26359896471</v>
+        <v>45708768794</v>
       </c>
       <c r="B15" t="s">
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D15" t="s">
         <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>41450539758</v>
+        <v>62954400517</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
         <v>6</v>
       </c>
       <c r="D16" s="1">
-        <v>19543</v>
+        <v>19879</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
@@ -797,87 +803,87 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>90389510838</v>
+        <v>41956135383</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
         <v>6</v>
       </c>
-      <c r="D17" t="s">
-        <v>33</v>
+      <c r="D17" s="1">
+        <v>17326</v>
       </c>
       <c r="E17" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>84979377943</v>
+        <v>82093739452</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D18" t="s">
         <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>49007797518</v>
+        <v>40512895825</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="1">
-        <v>21738</v>
+      <c r="D19" t="s">
+        <v>36</v>
       </c>
       <c r="E19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>80897969097</v>
+        <v>75685655389</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="1">
-        <v>20790</v>
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>37</v>
       </c>
       <c r="E20" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>29601590244</v>
+        <v>41494301421</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D21" s="1">
-        <v>20036</v>
+        <v>15713</v>
       </c>
       <c r="E21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -886,7 +892,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03460479-F27D-4255-B8F6-E81F1B00703E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65944DDC-145B-49EA-8593-4282CE9DC120}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
